--- a/artfynd/A 16857-2025 artfynd.xlsx
+++ b/artfynd/A 16857-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137034056</v>
       </c>
       <c r="B2" t="n">
-        <v>79504</v>
+        <v>79506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16857-2025 artfynd.xlsx
+++ b/artfynd/A 16857-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137034056</v>
       </c>
       <c r="B2" t="n">
-        <v>79506</v>
+        <v>79507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16857-2025 artfynd.xlsx
+++ b/artfynd/A 16857-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137034056</v>
       </c>
       <c r="B2" t="n">
-        <v>79507</v>
+        <v>79509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16857-2025 artfynd.xlsx
+++ b/artfynd/A 16857-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137034056</v>
       </c>
       <c r="B2" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16857-2025 artfynd.xlsx
+++ b/artfynd/A 16857-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137034056</v>
       </c>
       <c r="B2" t="n">
-        <v>79512</v>
+        <v>79525</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16857-2025 artfynd.xlsx
+++ b/artfynd/A 16857-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137034056</v>
       </c>
       <c r="B2" t="n">
-        <v>79525</v>
+        <v>79527</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16857-2025 artfynd.xlsx
+++ b/artfynd/A 16857-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137034056</v>
       </c>
       <c r="B2" t="n">
-        <v>79527</v>
+        <v>79537</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16857-2025 artfynd.xlsx
+++ b/artfynd/A 16857-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137034056</v>
       </c>
       <c r="B2" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16857-2025 artfynd.xlsx
+++ b/artfynd/A 16857-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137034056</v>
       </c>
       <c r="B2" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16857-2025 artfynd.xlsx
+++ b/artfynd/A 16857-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137034056</v>
       </c>
       <c r="B2" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16857-2025 artfynd.xlsx
+++ b/artfynd/A 16857-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137034056</v>
       </c>
       <c r="B2" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16857-2025 artfynd.xlsx
+++ b/artfynd/A 16857-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137034056</v>
       </c>
       <c r="B2" t="n">
-        <v>79557</v>
+        <v>79559</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16857-2025 artfynd.xlsx
+++ b/artfynd/A 16857-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137034056</v>
       </c>
       <c r="B2" t="n">
-        <v>79559</v>
+        <v>79563</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
